--- a/Arquivos_QHG/dados_acareacoes_QHG.xlsx
+++ b/Arquivos_QHG/dados_acareacoes_QHG.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320058508700</t>
+          <t>3320089939440</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,44 +481,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>julinha</t>
+          <t>Alexsiane Moreira Pires</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5531987533232</t>
+          <t>+5531988850825</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rua Luiz Elias de Medeiros 133 casa 1, Sete Lagoas</t>
+          <t>Rua Edson Soares de Oliveira 167 Casa, Sete Lagoas</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Minhoca Antiestresse Colorida Brinquedo Sensorial Articulado*1</t>
+          <t>Tênis Casual Feminino Chucky Plataforma Adulto Confortavel*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>62.87</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:21:52</t>
+          <t>2026-09-10 13:33:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320055499966</t>
+          <t>3320050919013</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(STL INT) Brena Pereira (Matozinhos)</t>
+          <t>(STL LOC) Rafael Aparecido</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,32 +528,455 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Isabella Eduarda</t>
+          <t>mariaaparecidadas2515</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5531997827143</t>
+          <t>+5531988169445</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rua Eduardo Gonçalves Cotta 650, Matozinhos</t>
+          <t>Rua Ângelo Vieira Martins 406 casa, Sete Lagoas</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A.Chinelo Slide Feminino Nuvem Conforto Acolchoado Calçado Confortável Moda Praia Antiderrapante EVA Flip Flops slippers that says mom 2*1</t>
+          <t>Kit Petisqueira 3un + 3un Cumbuca coração plástico resistente Cor Branco*2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-08 12:10:26</t>
+          <t>2026-09-10 12:13:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3320044932746</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(STL LOC) Fabricio Braga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pedro Henrique</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+5531997594004</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rua Otoni Alves Costa 339, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cebolinha Jequiti Perfume Deo Colônia 25ml - Turma Da Mônica 100% Original!*1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>28.91</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:11:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3320003947411</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(STL LOC) Cynthia Franciele</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hugo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+5553198118577</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rua Noel Rosa 452 Casa Portao preto, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TB Moda conjunto Cordão Corrente Moeda Antiga Masculino Pingente Pulseira*1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:09:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3320098790175</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(STL LOC) Mateus Felipe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dyj4xjytpmpt</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+5531984104776</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rua Coromandel 401 casa, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Colar crucifixo cruz antiga vintage*1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7.74</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3320057901393</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(STL LOC) Joneslon Lopes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>glaucienefernand5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+5531998878329</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Avenida Cornélio Viana 1402, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rasteirinha Feminina Gotinha Sandália Plana Preta Branca Nude Dourada Rasteira com Brilho*1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10.77</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:42:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3320047919927</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>(STL LOC) Marislania de Jesus Rosa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tamara talita</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+5531995948706</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rua Ipameri 21, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Babuche Feminina Plataforma EVA com Enfeites de Strass e Pérolas - Chinelo Tamanco Confortável,Macio e Respirável para Praia e Piscina Cano curto, antiderrapante e muito confortável*1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:42:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3320088906237</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(STL LOC) Lucas Trindade Oliveira</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mirian Ferreira</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+5531999634520</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rua Jose Omar Guimarães 179, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kit 2 Lápis de Olho e Sobrancelha Preto e Marrom Profissional Vivai com Apontador Longa Duração Maquiagem Delineador*1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12.98</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3320007937271</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(STL LOC) Lorayne Luciene</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Catia Marques fonseca</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+5531993987017</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rua Eponina Soares Santos 465 Casa 2, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Massa Resina Termoplástica PCL Moldável Reutilizável Polycaprolactona Gramas Artesanato Restauração*1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3320066931356</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(STL LOC) Marislania de Jesus Rosa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lorena Maria</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+5531995287741</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Avenida Vicente Lopes da Rocha 253, Sete Lagoas</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KIT 3: Baby Tee Feminina - Blusa Slim Fit Manga Curta - Blusa de Compressão - Blusa Feminina*1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>33.68</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:30:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3320085912981</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(STL INT) Eduardo Francisco (P.Leopoldo)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Andréia Lucia Pereira</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+5531998220304</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rua José Pereira da Silva 41 AP 201, Pedro Leopoldo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Grampo de cabelo pequeno cereja, pequeno, requintado e fofo*1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:37:05</t>
         </is>
       </c>
     </row>
